--- a/WorkBot/refactor-experimental/data/orders/Copper Horse Coffee/Copper Horse Coffee_Downtown_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Copper Horse Coffee/Copper Horse Coffee_Downtown_20251114.xlsx
@@ -450,20 +450,14 @@
           <t>Copper Horse - Warhorse 5lb</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>55.99</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>55.99</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>55.99</v>
+      </c>
+      <c r="E2" t="n">
+        <v>55.99</v>
       </c>
     </row>
     <row r="3">
@@ -473,20 +467,14 @@
           <t>Copper Horse - Carriage House Blend (12oz)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>10.89</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>43.56</t>
-        </is>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="E3" t="n">
+        <v>43.56</v>
       </c>
     </row>
     <row r="4">
@@ -496,20 +484,14 @@
           <t>Copper Horse - Hayride</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>10.89</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>43.56</t>
-        </is>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="E4" t="n">
+        <v>43.56</v>
       </c>
     </row>
     <row r="5">
@@ -519,20 +501,14 @@
           <t>Copper Horse - Sleigh Bells (12oz)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>9.79</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>29.37</t>
-        </is>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="E5" t="n">
+        <v>29.37</v>
       </c>
     </row>
     <row r="6">
@@ -542,20 +518,14 @@
           <t>Copper Horse - Tanzania (12oz)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>10.89</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>32.67</t>
-        </is>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="E6" t="n">
+        <v>32.67</v>
       </c>
     </row>
   </sheetData>
